--- a/testdata/FlightDetails.xlsx
+++ b/testdata/FlightDetails.xlsx
@@ -38,6 +38,24 @@
     <t>IndiGo</t>
   </si>
   <si>
+    <t>6E-796</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>02:50</t>
+  </si>
+  <si>
+    <t>4h 50m</t>
+  </si>
+  <si>
+    <t>Partial Refundable</t>
+  </si>
+  <si>
+    <t>₹5,627</t>
+  </si>
+  <si>
     <t>6E-6081</t>
   </si>
   <si>
@@ -50,22 +68,16 @@
     <t>6h 15m</t>
   </si>
   <si>
-    <t>Partial Refundable</t>
-  </si>
-  <si>
-    <t>₹5,627</t>
-  </si>
-  <si>
-    <t>6E-495</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>3h 45m</t>
+    <t>6E-193</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>5h</t>
   </si>
   <si>
     <t>₹5,759</t>
@@ -116,58 +128,46 @@
     <t>08:45</t>
   </si>
   <si>
+    <t>6E-6225</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>6E-5149</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>2h 5m</t>
+  </si>
+  <si>
     <t>6E-244</t>
   </si>
   <si>
     <t>03:55</t>
   </si>
   <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>5h 40m</t>
+  </si>
+  <si>
+    <t>₹5,837</t>
+  </si>
+  <si>
     <t>10:30</t>
   </si>
   <si>
     <t>6h 35m</t>
-  </si>
-  <si>
-    <t>₹5,837</t>
-  </si>
-  <si>
-    <t>3h 50m</t>
-  </si>
-  <si>
-    <t>₹5,857</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>9h 35m</t>
-  </si>
-  <si>
-    <t>6E-2133</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>1h 45m</t>
-  </si>
-  <si>
-    <t>₹6,059</t>
-  </si>
-  <si>
-    <t>6E-6225</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>₹6,220</t>
   </si>
 </sst>
 </file>
@@ -281,7 +281,7 @@
         <v>12</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -289,22 +289,22 @@
         <v>7</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="D4" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="D4" t="s" s="0">
+      <c r="E4" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="E4" t="s" s="0">
+      <c r="F4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s" s="0">
         <v>22</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -327,7 +327,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -335,13 +335,13 @@
         <v>7</v>
       </c>
       <c r="B6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="D6" t="s" s="0">
         <v>29</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>21</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>30</v>
@@ -350,7 +350,7 @@
         <v>12</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -358,22 +358,22 @@
         <v>7</v>
       </c>
       <c r="B7" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s" s="0">
         <v>31</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -381,22 +381,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="C8" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>37</v>
-      </c>
       <c r="F8" t="s" s="0">
         <v>12</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -404,22 +404,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s" s="0">
         <v>12</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -427,22 +427,22 @@
         <v>7</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s" s="0">
         <v>12</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -450,22 +450,22 @@
         <v>7</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s" s="0">
         <v>12</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -473,22 +473,22 @@
         <v>7</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>50</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="F12" t="s" s="0">
         <v>12</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/FlightDetails.xlsx
+++ b/testdata/FlightDetails.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
   <si>
     <t>Airline</t>
   </si>
@@ -38,84 +38,33 @@
     <t>IndiGo</t>
   </si>
   <si>
-    <t>6E-796</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>02:50</t>
-  </si>
-  <si>
-    <t>4h 50m</t>
+    <t>6E-5093</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>1h 55m</t>
   </si>
   <si>
     <t>Partial Refundable</t>
   </si>
   <si>
-    <t>₹5,627</t>
-  </si>
-  <si>
-    <t>6E-6081</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>6h 15m</t>
-  </si>
-  <si>
-    <t>6E-193</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>5h</t>
-  </si>
-  <si>
-    <t>₹5,759</t>
-  </si>
-  <si>
-    <t>6E-341</t>
-  </si>
-  <si>
-    <t>22:35</t>
+    <t>₹5,829</t>
+  </si>
+  <si>
+    <t>6E-6140</t>
+  </si>
+  <si>
+    <t>02:30</t>
   </si>
   <si>
     <t>04:30</t>
   </si>
   <si>
-    <t>5h 55m</t>
-  </si>
-  <si>
-    <t>6E-5093</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>1h 55m</t>
-  </si>
-  <si>
-    <t>₹5,829</t>
-  </si>
-  <si>
-    <t>6E-6140</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
     <t>2h</t>
   </si>
   <si>
@@ -149,25 +98,19 @@
     <t>2h 5m</t>
   </si>
   <si>
-    <t>6E-244</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>5h 40m</t>
-  </si>
-  <si>
-    <t>₹5,837</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>6h 35m</t>
+    <t>6E-2133</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>1h 45m</t>
+  </si>
+  <si>
+    <t>₹6,059</t>
   </si>
 </sst>
 </file>
@@ -212,7 +155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -298,13 +241,13 @@
         <v>20</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>12</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -312,22 +255,22 @@
         <v>7</v>
       </c>
       <c r="B5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="C5" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>25</v>
-      </c>
       <c r="E5" t="s" s="0">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>12</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -335,22 +278,22 @@
         <v>7</v>
       </c>
       <c r="B6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="C6" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>30</v>
-      </c>
       <c r="F6" t="s" s="0">
         <v>12</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -358,137 +301,22 @@
         <v>7</v>
       </c>
       <c r="B7" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s" s="0">
         <v>32</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="F8" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G9" t="s" s="0">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="F10" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s" s="0">
-        <v>48</v>
-      </c>
-      <c r="F11" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G11" t="s" s="0">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s" s="0">
-        <v>51</v>
-      </c>
-      <c r="F12" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G12" t="s" s="0">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
